--- a/docs/girl_star_economy.xlsx
+++ b/docs/girl_star_economy.xlsx
@@ -2067,27 +2067,27 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>①先鋒 ＋ ②引路 ＋ ⑥斷鉗 ＋ ⑧負行</t>
+          <t>免死組：①先鋒 ＋ ②引路 ＋ ④堅殼 ＋ ⑦蟹生</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>1+1+3+4＝9</t>
+          <t>1+1+2+4＝8</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>聖徒化開場血 1（時間最長）＋挨打不推進倒數 ⇒ 幾乎每次都 Maximum Burst。</t>
+          <t>天鎖每隻怪一次（⑦）＋天鎖十秒內射擊回血（④）＋失誤一次不受擊（②）。方案 D 約 Lv5 就湊得齊（不必改排列）。聖徒化那一路（⑥斷鉗＋⑧負行，7 份）是後期上限：一場一次、幾乎穩出 MB。</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>低：強度要 7 份才成形，前期仍是三人最弱。</t>
+          <t>低。⚠ 單體 Boss 只有一場 ⇒ ⑦蟹生在 Boss 戰沒有作用，手殘玩家在 Boss 前只有「一次免死＋回血」。</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>【Ray 方向：早期就進入穩定的不死狀態，保護手殘玩家】不死的三顆是 ④堅殼（天鎖期間射擊回血）、⑦蟹生（天鎖每一隻怪一次）、②引路（失誤一次不受擊）。建議把 ⑦蟹生換到 ② 或 ③、④堅殼留在 ④ ⇒ 1+1+2＋2＝6 份（方案 D 約 Lv4）就是「每隻怪一次免死＋十秒回血」；被換下來的 ②引路／③探覓往後挪。聖徒化那一路（⑥⑧）維持高價當後期的上限。</t>
+          <t>【Ray 方向：早期穩定不死】要在 Boss 戰也「穩定」，④堅殼的回血是關鍵（已在 2 份的位置）；若還不夠，可讓天鎖在同一場有第二次（例如 ⑦ 改成「每一場兩次」）或把回血比例提高。</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>③烙印 ＋ ⑥前引 ＋ ⑦界心</t>
+          <t>③烙印 ＋ ⑥前引 ＋ ⑧界心</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>③ 只要 2 份就能「3 次完美反擊回填夢魘化」，每回填一次＝再一發敵最大 HP 20% 固定傷害。</t>
+          <t>回填改成下一場之後，③烙印只在連戰有用；Boss 戰一場只有一發夢境粉碎（20%，⑧ 之後 30%）。</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>高：最便宜就能質變，對 Boss 的傷害不吃技術。</t>
+          <t>中→低（-1775 之前是最高）。連戰清雜怪時仍強：粉碎打死＝處決＝下一隻又能開夢魘化，可以一路串。</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>③ 換到更後面的位置（至少 ⑤）；或烙印星改成「一局最多回填 1 次」。</t>
+          <t>已大致平衡。要再收只收連戰：例如粉碎處決不賺回發動（只留烙印星那條路）。</t>
         </is>
       </c>
     </row>
@@ -2141,17 +2141,17 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>戰吼→主動技→回填共鬥 ⇒ 無敵共鬥可以一直循環；② 只要 1 份。</t>
+          <t>⑦聚落「主動技回填共鬥」是**唯一還能在同一場再開一次**的變身：戰吼→主動技→共鬥，Boss 戰可以開好幾次無敵共鬥。</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>高：接近打不死，又有評價寬限＋EXP 反向（升得最快）。</t>
+          <t>高：現在三人裡唯一的例外，Boss 戰差距最大；又有評價寬限＋EXP 反向（升得最快）。</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>② 海宣星往後挪；或聚落星回填的共鬥時長吃當下破防值、不給滿值。</t>
+          <t>把 ⑦聚落也改成「下一場才生效」（與 SI／NI 同一條規則，走同一對 defer／apply）；②海宣（回填主動技）可以留著當她的同場循環。</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>價格跟著「位置」走（①② 最便宜），而安雅 ③、索菈娜 ② 這兩顆剛好是會形成循環或陡升的星 —— 失衡主要來自「強的星放在便宜的位置」。收入調到方案 D 之後，中階大約 4 顆、跳著挑就是 9 份以內的組合，上表三組正好都買得起：安雅與索菈娜在中段就成形，諾薇兒要到後段。</t>
+          <t>前提（ver -1775）：聖徒化／夢魘化一場限一次，回填一律下一場才生效；星不用等級鎖，價格 1/1/2/2/3/3/4/4＋⑨條件。⇒ 單體 Boss 戰三人都只有「一次變身」，差距回到技能本身；安雅的便宜強星（③烙印）只剩連戰價值。現在唯一的例外是索菈娜 ⑦聚落（同一場再開共鬥），建議比照同一條規則。諾薇兒的免死組在方案 D 約 Lv5 可成形，但 Boss 戰只有一次免死。</t>
         </is>
       </c>
     </row>

--- a/docs/girl_star_economy.xlsx
+++ b/docs/girl_star_economy.xlsx
@@ -2141,17 +2141,17 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>⑦聚落「主動技回填共鬥」是**唯一還能在同一場再開一次**的變身：戰吼→主動技→共鬥，Boss 戰可以開好幾次無敵共鬥。</t>
+          <t>⑦聚落讓共鬥同一場可以再開，但共鬥**消耗全部破防值**、時長＝12 秒×破防值/100（最低 3 秒），期間普攻回充只有一半 ⇒ 連開的無敵時間被破防值總量封頂，而那正是彈雨的輸出來源。</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>高：現在三人裡唯一的例外，Boss 戰差距最大；又有評價寬限＋EXP 反向（升得最快）。</t>
+          <t>低（Ray 的設計，-1775 後確認）：連開共鬥＝輸出下降、局變長，而她的評價時間係數是 650（別人 400）⇒ 必定低評（錢是敵 HP×等第%，D 只拿 50%）。低評反而給她較多 EXP 與好感 —— 那是她「打得爛也開心」的性格，是取捨不是漏洞。</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>把 ⑦聚落也改成「下一場才生效」（與 SI／NI 同一條規則，走同一對 defer／apply）；②海宣（回填主動技）可以留著當她的同場循環。</t>
+          <t>不改。⚠ 唯一要留意：保守玩法會讓她升得最快（EXP 反向），如果不想她領先太多，調的是 EXP 而不是共鬥。</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>前提（ver -1775）：聖徒化／夢魘化一場限一次，回填一律下一場才生效；星不用等級鎖，價格 1/1/2/2/3/3/4/4＋⑨條件。⇒ 單體 Boss 戰三人都只有「一次變身」，差距回到技能本身；安雅的便宜強星（③烙印）只剩連戰價值。現在唯一的例外是索菈娜 ⑦聚落（同一場再開共鬥），建議比照同一條規則。諾薇兒的免死組在方案 D 約 Lv5 可成形，但 Boss 戰只有一次免死。</t>
+          <t>前提（ver -1775）：聖徒化／夢魘化一場限一次，回填一律下一場才生效；星不用等級鎖，價格 1/1/2/2/3/3/4/4＋⑨條件。⇒ 單體 Boss 戰三人都只有「一次變身」，差距回到技能本身；安雅的便宜強星（③烙印）只剩連戰價值。索菈娜 ⑦聚落雖然同一場能再開共鬥，但被破防值總量與評價係數 650 綁住（連開＝必定低評），Ray 定為刻意的取捨，不改。諾薇兒的免死組在方案 D 約 Lv5 可成形，但 Boss 戰只有一次免死。</t>
         </is>
       </c>
     </row>

--- a/docs/girl_star_economy.xlsx
+++ b/docs/girl_star_economy.xlsx
@@ -2151,7 +2151,7 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>不改。⚠ 唯一要留意：保守玩法會讓她升得最快（EXP 反向），如果不想她領先太多，調的是 EXP 而不是共鬥。</t>
+          <t>不改。她**沒有任何回血手段**（共鬥只擋不補），連戰會被慢慢耗死 ⇒ 保守型玩家會選諾薇兒不是她（Ray），「保守玩法讓她升最快」不成立。</t>
         </is>
       </c>
     </row>

--- a/docs/girl_star_economy.xlsx
+++ b/docs/girl_star_economy.xlsx
@@ -505,14 +505,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>規則（Ray 定案）：星不再用等級鎖。①② 各 1 份、③④ 各 2 份、⑤⑥ 各 3 份、⑦⑧ 各 4 份；⑨＝滿足特定條件（不花紀錄）。</t>
+          <t>規則（Ray 定案）：星不再用等級鎖、等級上限 20。①出場就亮、② 1 份、③④ 各 2 份、⑤⑥ 各 3 份、⑦⑧ 各 4 份；⑨＝滿足特定條件（不花紀錄）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>⇒ ①～⑧ 全亮總共要 20 份。等級只負責「產出」紀錄。</t>
+          <t>⇒ ②～⑧ 總共 19 份＝Lv1→Lv20 升 19 級的 19 份，滿級剛好全亮。等級只負責「產出」紀錄。</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <f>SUM($B$2:B2)</f>
@@ -1196,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1308,7 +1308,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="C3">
         <f>ROUND(B3/參數!$B$12,1)</f>
@@ -1348,7 +1348,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3800</v>
+        <v>1700</v>
       </c>
       <c r="C4">
         <f>ROUND(B4/參數!$B$12,1)</f>
@@ -1388,7 +1388,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7000</v>
+        <v>2700</v>
       </c>
       <c r="C5">
         <f>ROUND(B5/參數!$B$12,1)</f>
@@ -1428,7 +1428,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>11500</v>
+        <v>3800</v>
       </c>
       <c r="C6">
         <f>ROUND(B6/參數!$B$12,1)</f>
@@ -1468,7 +1468,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>17500</v>
+        <v>5050</v>
       </c>
       <c r="C7">
         <f>ROUND(B7/參數!$B$12,1)</f>
@@ -1508,7 +1508,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>25500</v>
+        <v>6450</v>
       </c>
       <c r="C8">
         <f>ROUND(B8/參數!$B$12,1)</f>
@@ -1548,7 +1548,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>36000</v>
+        <v>8050</v>
       </c>
       <c r="C9">
         <f>ROUND(B9/參數!$B$12,1)</f>
@@ -1588,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>50000</v>
+        <v>9800</v>
       </c>
       <c r="C10">
         <f>ROUND(B10/參數!$B$12,1)</f>
@@ -1623,8 +1623,448 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>11800</v>
+      </c>
+      <c r="C11">
+        <f>ROUND(B11/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>ROUND(B11/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>(A11-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>FLOOR(C11*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>E11+F11</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G11))</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>E11+FLOOR(D11*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I11))</f>
+        <v/>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C12">
+        <f>ROUND(B12/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>ROUND(B12/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>(A12-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>FLOOR(C12*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>E12+F12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G12))</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>E12+FLOOR(D12*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C13">
+        <f>ROUND(B13/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>ROUND(B13/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>(A13-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>FLOOR(C13*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>E13+F13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G13))</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>E13+FLOOR(D13*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>19300</v>
+      </c>
+      <c r="C14">
+        <f>ROUND(B14/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>ROUND(B14/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>(A14-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>FLOOR(C14*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>E14+F14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G14))</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>E14+FLOOR(D14*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J14">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>22400</v>
+      </c>
+      <c r="C15">
+        <f>ROUND(B15/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>ROUND(B15/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>(A15-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>FLOOR(C15*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>E15+F15</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G15))</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>E15+FLOOR(D15*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J15">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>25900</v>
+      </c>
+      <c r="C16">
+        <f>ROUND(B16/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>ROUND(B16/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>(A16-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>FLOOR(C16*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>E16+F16</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G16))</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>E16+FLOOR(D16*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J16">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>29800</v>
+      </c>
+      <c r="C17">
+        <f>ROUND(B17/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>ROUND(B17/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>(A17-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>FLOOR(C17*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>E17+F17</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G17))</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>E17+FLOOR(D17*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J17">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>34200</v>
+      </c>
+      <c r="C18">
+        <f>ROUND(B18/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>ROUND(B18/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>(A18-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>FLOOR(C18*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>E18+F18</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G18))</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>E18+FLOOR(D18*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J18">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>39100</v>
+      </c>
+      <c r="C19">
+        <f>ROUND(B19/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>ROUND(B19/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>(A19-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>FLOOR(C19*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>E19+F19</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G19))</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>E19+FLOOR(D19*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>44600</v>
+      </c>
+      <c r="C20">
+        <f>ROUND(B20/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>ROUND(B20/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>(A20-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>FLOOR(C20*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>E20+F20</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G20))</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>E20+FLOOR(D20*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>50750</v>
+      </c>
+      <c r="C21">
+        <f>ROUND(B21/參數!$B$12,1)</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>ROUND(B21/參數!$B$13,1)</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>(A21-1)*參數!$B$2</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>FLOOR(C21*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>E21+F21</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G21))</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>E21+FLOOR(D21*參數!$B$4,1)*參數!$B$3</f>
+        <v/>
+      </c>
+      <c r="J21">
+        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>⚠ 「劇情固定給」沒有攤進逐級（不知道哪一章在哪一級），看「方案比較」那一頁的合計。</t>
         </is>
@@ -1644,10 +2084,10 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -1677,47 +2117,47 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>劇情合計</t>
+          <t>出廠／固定給</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Lv3 份數</t>
+          <t>Lv5 份數</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Lv3 顆</t>
+          <t>Lv5 顆</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Lv5 份數</t>
+          <t>Lv10 份數</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Lv5 顆</t>
+          <t>Lv10 顆</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Lv7 份數</t>
+          <t>Lv15 份數</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Lv7 顆</t>
+          <t>Lv15 顆</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Lv9 份數</t>
+          <t>Lv20 份數</t>
         </is>
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t>Lv9 顆</t>
+          <t>Lv20 顆</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -1727,9 +2167,9 @@
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>A 現值</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>A 現值（每級 1、①出場就亮）</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
@@ -1741,61 +2181,61 @@
       <c r="D2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E2">
-        <f>(3-1)*B2+FLOOR('升級與收入'!C4*參數!$B$4,1)*C2+0</f>
-        <v/>
-      </c>
-      <c r="F2">
+      <c r="E2" s="10">
+        <f>(5-1)*B2+FLOOR('升級與收入'!C6*參數!$B$4,1)*C2+D2</f>
+        <v/>
+      </c>
+      <c r="F2" s="10">
         <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=E2))</f>
         <v/>
       </c>
-      <c r="G2">
-        <f>(5-1)*B2+FLOOR('升級與收入'!C6*參數!$B$4,1)*C2+0</f>
-        <v/>
-      </c>
-      <c r="H2">
+      <c r="G2" s="10">
+        <f>(10-1)*B2+FLOOR('升級與收入'!C11*參數!$B$4,1)*C2+D2</f>
+        <v/>
+      </c>
+      <c r="H2" s="10">
         <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G2))</f>
         <v/>
       </c>
-      <c r="I2">
-        <f>(7-1)*B2+FLOOR('升級與收入'!C8*參數!$B$4,1)*C2+0</f>
-        <v/>
-      </c>
-      <c r="J2">
+      <c r="I2" s="10">
+        <f>(15-1)*B2+FLOOR('升級與收入'!C16*參數!$B$4,1)*C2+D2</f>
+        <v/>
+      </c>
+      <c r="J2" s="10">
         <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I2))</f>
         <v/>
       </c>
-      <c r="K2">
-        <f>(9-1)*B2+FLOOR('升級與收入'!C10*參數!$B$4,1)*C2+D2</f>
-        <v/>
-      </c>
-      <c r="L2">
+      <c r="K2" s="10">
+        <f>(20-1)*B2+FLOOR('升級與收入'!C21*參數!$B$4,1)*C2+D2</f>
+        <v/>
+      </c>
+      <c r="L2" s="10">
         <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=K2))</f>
         <v/>
       </c>
-      <c r="M2" s="7" t="inlineStr">
-        <is>
-          <t>中階（Lv5）3 顆、滿級 4 顆：⑤ 以後幾乎摸不到，「選」變成「只能點前面」。</t>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>【定案】Lv20 升 19 級＝19 份＝②～⑧ 剛好全亮。Lv5 手上 4 份＝諾薇兒 ②引路＋④堅殼（①已亮）還剩 1。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>B 每級 2 份</t>
+          <t>B 每級 1＋Boss 局 1 份</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E3">
-        <f>(3-1)*B3+FLOOR('升級與收入'!C4*參數!$B$4,1)*C3+0</f>
+        <f>(5-1)*B3+FLOOR('升級與收入'!C6*參數!$B$4,1)*C3+D3</f>
         <v/>
       </c>
       <c r="F3">
@@ -1803,7 +2243,7 @@
         <v/>
       </c>
       <c r="G3">
-        <f>(5-1)*B3+FLOOR('升級與收入'!C6*參數!$B$4,1)*C3+0</f>
+        <f>(10-1)*B3+FLOOR('升級與收入'!C11*參數!$B$4,1)*C3+D3</f>
         <v/>
       </c>
       <c r="H3">
@@ -1811,7 +2251,7 @@
         <v/>
       </c>
       <c r="I3">
-        <f>(7-1)*B3+FLOOR('升級與收入'!C8*參數!$B$4,1)*C3+0</f>
+        <f>(15-1)*B3+FLOOR('升級與收入'!C16*參數!$B$4,1)*C3+D3</f>
         <v/>
       </c>
       <c r="J3">
@@ -1819,7 +2259,7 @@
         <v/>
       </c>
       <c r="K3">
-        <f>(9-1)*B3+FLOOR('升級與收入'!C10*參數!$B$4,1)*C3+D3</f>
+        <f>(20-1)*B3+FLOOR('升級與收入'!C21*參數!$B$4,1)*C3+D3</f>
         <v/>
       </c>
       <c r="L3">
@@ -1828,27 +2268,27 @@
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>中階 4 顆、滿級 7 顆：⑧ 要靠劇情或條件補。</t>
+          <t>滿級前就全亮；Boss 越多的路線越快（變成鼓勵刷 Boss）。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>C 每級 2 份＋Boss 1 份</t>
+          <t>C 每級 2</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E4">
-        <f>(3-1)*B4+FLOOR('升級與收入'!C4*參數!$B$4,1)*C4+0</f>
+        <f>(5-1)*B4+FLOOR('升級與收入'!C6*參數!$B$4,1)*C4+D4</f>
         <v/>
       </c>
       <c r="F4">
@@ -1856,7 +2296,7 @@
         <v/>
       </c>
       <c r="G4">
-        <f>(5-1)*B4+FLOOR('升級與收入'!C6*參數!$B$4,1)*C4+0</f>
+        <f>(10-1)*B4+FLOOR('升級與收入'!C11*參數!$B$4,1)*C4+D4</f>
         <v/>
       </c>
       <c r="H4">
@@ -1864,7 +2304,7 @@
         <v/>
       </c>
       <c r="I4">
-        <f>(7-1)*B4+FLOOR('升級與收入'!C8*參數!$B$4,1)*C4+0</f>
+        <f>(15-1)*B4+FLOOR('升級與收入'!C16*參數!$B$4,1)*C4+D4</f>
         <v/>
       </c>
       <c r="J4">
@@ -1872,7 +2312,7 @@
         <v/>
       </c>
       <c r="K4">
-        <f>(9-1)*B4+FLOOR('升級與收入'!C10*參數!$B$4,1)*C4+D4</f>
+        <f>(20-1)*B4+FLOOR('升級與收入'!C21*參數!$B$4,1)*C4+D4</f>
         <v/>
       </c>
       <c r="L4">
@@ -1881,120 +2321,14 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>Lv5 就 6 顆、Lv7 全亮：Boss 越多的路線越快（變成鼓勵刷 Boss）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>D 每級 2 份＋劇情 4 份</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="10">
-        <f>(3-1)*B5+FLOOR('升級與收入'!C4*參數!$B$4,1)*C5+0</f>
-        <v/>
-      </c>
-      <c r="F5" s="10">
-        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=E5))</f>
-        <v/>
-      </c>
-      <c r="G5" s="10">
-        <f>(5-1)*B5+FLOOR('升級與收入'!C6*參數!$B$4,1)*C5+0</f>
-        <v/>
-      </c>
-      <c r="H5" s="10">
-        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G5))</f>
-        <v/>
-      </c>
-      <c r="I5" s="10">
-        <f>(7-1)*B5+FLOOR('升級與收入'!C8*參數!$B$4,1)*C5+0</f>
-        <v/>
-      </c>
-      <c r="J5" s="10">
-        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I5))</f>
-        <v/>
-      </c>
-      <c r="K5" s="10">
-        <f>(9-1)*B5+FLOOR('升級與收入'!C10*參數!$B$4,1)*C5+D5</f>
-        <v/>
-      </c>
-      <c r="L5" s="10">
-        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=K5))</f>
-        <v/>
-      </c>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>【建議】中階 4 顆可選、主線打完剛好 ①～⑧ 全亮（20 份）；進度由劇情控，不靠刷。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>E 每級 3 份</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <f>(3-1)*B6+FLOOR('升級與收入'!C4*參數!$B$4,1)*C6+0</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=E6))</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>(5-1)*B6+FLOOR('升級與收入'!C6*參數!$B$4,1)*C6+0</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=G6))</f>
-        <v/>
-      </c>
-      <c r="I6">
-        <f>(7-1)*B6+FLOOR('升級與收入'!C8*參數!$B$4,1)*C6+0</f>
-        <v/>
-      </c>
-      <c r="J6">
-        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=I6))</f>
-        <v/>
-      </c>
-      <c r="K6">
-        <f>(9-1)*B6+FLOOR('升級與收入'!C10*參數!$B$4,1)*C6+D6</f>
-        <v/>
-      </c>
-      <c r="L6">
-        <f>SUMPRODUCT(--(星價!$C$2:$C$9&lt;=K6))</f>
-        <v/>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>Lv5 就 6 顆、Lv9 全亮：太快，⑦⑧ 的強力循環會在中段就出現。</t>
+          <t>Lv10 前後就全亮：Lv20 那一大段等於沒有獎勵。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>⚠ 劇情合計只算進 Lv9 那一欄（假設劇情份數大多在後段給）；要看中段就把一部分改成 Boss 或每級。</t>
+          <t>⚠ ver -1776：等級上限 20（Ray）。「出廠／固定給」＝一開始就在手上的份數（每一欄都算進去）。</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2411,7 @@
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>天鎖每隻怪一次（⑦）＋天鎖十秒內射擊回血（④）＋失誤一次不受擊（②）。方案 D 約 Lv5 就湊得齊（不必改排列）。聖徒化那一路（⑥斷鉗＋⑧負行，7 份）是後期上限：一場一次、幾乎穩出 MB。</t>
+          <t>天鎖每隻怪一次（⑦）＋天鎖十秒內射擊回血（④）＋失誤一次不受擊（②）。Lv20 制約 Lv9 湊得齊 8 份（不必改排列）。聖徒化那一路（⑥斷鉗＋⑧負行，7 份）是後期上限：一場一次、幾乎穩出 MB。</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
@@ -2165,7 +2499,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>前提（ver -1775）：聖徒化／夢魘化一場限一次，回填一律下一場才生效；星不用等級鎖，價格 1/1/2/2/3/3/4/4＋⑨條件。⇒ 單體 Boss 戰三人都只有「一次變身」，差距回到技能本身；安雅的便宜強星（③烙印）只剩連戰價值。索菈娜 ⑦聚落雖然同一場能再開共鬥，但被破防值總量與評價係數 650 綁住（連開＝必定低評），Ray 定為刻意的取捨，不改。諾薇兒的免死組在方案 D 約 Lv5 可成形，但 Boss 戰只有一次免死。</t>
+          <t>前提（ver -1775）：聖徒化／夢魘化一場限一次，回填一律下一場才生效；星不用等級鎖，價格 1/1/2/2/3/3/4/4＋⑨條件。⇒ 單體 Boss 戰三人都只有「一次變身」，差距回到技能本身；安雅的便宜強星（③烙印）只剩連戰價值。索菈娜 ⑦聚落雖然同一場能再開共鬥，但被破防值總量與評價係數 650 綁住（連開＝必定低評），Ray 定為刻意的取捨，不改。諾薇兒的免死三顆（4 份）約 Lv5 可成形，但 Boss 戰只有一次免死。</t>
         </is>
       </c>
     </row>

--- a/docs/girl_star_economy.xlsx
+++ b/docs/girl_star_economy.xlsx
@@ -942,107 +942,107 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
+          <t>箭頭星 Alnasl（被動）
+獵手的戰吼發動條件由連續5盤完美清盤降低為3盤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="62" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>★3</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <f>SUM($B$2:B4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>探覓星 Nahn（主動）
+發動彈雨傾洩可回復魂之歸所的使用次數。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>烙印星 Alhena（變身）
+連續三次完美反擊即回復夢魘化熔斷；同場戰鬥內不可連續使用。同戰役的次場戰鬥生效。</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>曳弦星 Ascella（主動）
+獵手的智慧發動後追加 10 秒破防值累積量 200%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>★4</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <f>SUM($B$2:B5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>堅殼星 Tegmine（被動）
+獄門天鎖的十秒免傷期間，每次射擊回復最大體力 5%。反擊一次算一發，聖徒化期間不作動。</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>赤足星 Tejat（被動）
+明晰之夢延長為 10 秒。明晰之夢與夢魘化期間的反擊威力升一階：黃圈打橘圈傷害、橘圈打紅圈傷害、紅圈全暴擊。</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>獵弓星 Kaus Media（變身）
+獵手的共鬥期間，自動反擊威力提升 50%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>★5</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <f>SUM($B$2:B6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>端首星 Guisuyi（變身）
+單場無傷擊殺即回復聖徒化熔斷；同場戰鬥內不可連續使用。同戰役的次場戰鬥生效。</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>赤爪星 Mebsuta（主動）
+連續十次反擊成功（不限圈色）即回填夢境破碎。</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
           <t>海宣星 Nunki（被動）
 獵手的戰吼發動時，可再次使用獵手的智慧。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>★3</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <f>SUM($B$2:B4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>探覓星 Nahn（主動）
-發動彈雨傾洩可回復魂之歸所的使用次數。</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>烙印星 Alhena（變身）
-連續三次完美反擊即回復夢魘化熔斷；同場戰鬥內不可連續使用。同戰役的次場戰鬥生效。</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>曳弦星 Ascella（主動）
-獵手的智慧發動後追加 10 秒破防值累積量 200%。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>★4</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <f>SUM($B$2:B5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>堅殼星 Tegmine（被動）
-獄門天鎖的十秒免傷期間，每次射擊回復最大體力 5%。反擊一次算一發，聖徒化期間不作動。</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>赤足星 Tejat（被動）
-明晰之夢延長為 10 秒，期間所有反擊攻擊力提升。</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>獵弓星 Kaus Media（變身）
-獵手的共鬥期間，自動反擊威力提升 50%。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>★5</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <f>SUM($B$2:B6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>端首星 Guisuyi（變身）
-單場無傷擊殺即回復聖徒化熔斷；同場戰鬥內不可連續使用。同戰役的次場戰鬥生效。</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>赤爪星 Mebsuta（主動）
-夢境破碎後的反擊增益期間，所有反擊攻擊力提升。</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>箭頭星 Alnasl（被動）
-獵手的戰吼發動條件由連續5盤完美清盤降低為3盤。</t>
-        </is>
-      </c>
-    </row>
     <row r="7" ht="62" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>鐵蹄星 Alzirr（被動）
-明晰之夢延長為 15 秒，期間所有反擊攻擊力提升。</t>
+明晰之夢延長為 15 秒。反擊威力再升一階：黃圈打紅圈傷害、橘圈全暴擊、紅圈兩倍傷害。</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>②海宣 ＋ ⑤箭頭 ＋ ⑦聚落 ＋ ①地弓</t>
+          <t>②箭頭 ＋ ⑤海宣 ＋ ⑦聚落（①出場就亮）</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>1+3+4+1＝9</t>
+          <t>1+3+4＝8</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">

--- a/docs/girl_star_economy.xlsx
+++ b/docs/girl_star_economy.xlsx
@@ -2401,27 +2401,27 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>免死組：①先鋒 ＋ ②引路 ＋ ④堅殼 ＋ ⑦蟹生</t>
+          <t>①先鋒（出場就亮）＋ ②引路 ＋ ④堅殼 ／ 之後 ⑥斷鉗 ＋ ⑦蟹生</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>1+1+2+4＝8</t>
+          <t>1+2 ＝3（Lv4）／再 3+4</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>天鎖每隻怪一次（⑦）＋天鎖十秒內射擊回血（④）＋失誤一次不受擊（②）。Lv20 制約 Lv9 湊得齊 8 份（不必改排列）。聖徒化那一路（⑥斷鉗＋⑧負行，7 份）是後期上限：一場一次、幾乎穩出 MB。</t>
+          <t>②④ 3 份（約 Lv4）就是「失誤不受擊＋天鎖回血」的免死組；⑦ 讓連戰每隻怪一次。Ray：②引路對真人玩家很有利，**②＋⑥斷鉗基本就是 MB 保證**（1+3＝4 份，約 Lv5）—— 中期輸出並不弱，只是不比安雅的爆發。</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>低。⚠ 單體 Boss 只有一場 ⇒ ⑦蟹生在 Boss 戰沒有作用，手殘玩家在 Boss 前只有「一次免死＋回血」。</t>
+          <t>低。</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>【Ray 方向：早期穩定不死】要在 Boss 戰也「穩定」，④堅殼的回血是關鍵（已在 2 份的位置）；若還不夠，可讓天鎖在同一場有第二次（例如 ⑦ 改成「每一場兩次」）或把回血比例提高。</t>
+          <t>保守型玩家的首選（Ray）。不改。</t>
         </is>
       </c>
     </row>
@@ -2433,27 +2433,27 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>③烙印 ＋ ⑥前引 ＋ ⑧界心</t>
+          <t>④赤足 ＋ ②築壩者 ＋ ⑤赤爪 ／ 之後 ⑦鐵蹄 ＋ ⑧界心</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>2+3+4＝9</t>
+          <t>2+1+3 ＝6（Lv7）</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>回填改成下一場之後，③烙印只在連戰有用；Boss 戰一場只有一發夢境粉碎（20%，⑧ 之後 30%）。</t>
+          <t>明晰之夢與夢魘化同一套：必中、威力照圈色，赤足／鐵蹄各升一階（紅圈最高兩倍）。夢境破碎一場一發（20%／30%）。非夢魘化的粉碎＝**固定 5 秒**的增益（Ray -1779：與 Boss 的密集圈對沖，不長駐）；赤爪星十連回填它。</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>中→低（-1775 之前是最高）。連戰清雜怪時仍強：粉碎打死＝處決＝下一隻又能開夢魘化，可以一路串。</t>
+          <t>中。增益期間必中的反擊不扣血 ⇒ 也有保命面，但 5 秒＋十連回填，上限有限。</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>已大致平衡。要再收只收連戰：例如粉碎處決不賺回發動（只留烙印星那條路）。</t>
+          <t>已定。</t>
         </is>
       </c>
     </row>
@@ -2465,27 +2465,27 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>②箭頭 ＋ ⑤海宣 ＋ ⑦聚落（①出場就亮）</t>
+          <t>②箭頭 ＋ ⑤海宣（＋ ⑦聚落）</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>1+3+4＝8</t>
+          <t>1+3 ＝4（Lv5）</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>⑦聚落讓共鬥同一場可以再開，但共鬥**消耗全部破防值**、時長＝12 秒×破防值/100（最低 3 秒），期間普攻回充只有一半 ⇒ 連開的無敵時間被破防值總量封頂，而那正是彈雨的輸出來源。</t>
+          <t>戰吼→彈雨→再戰吼的循環中期就成形 —— **刻意的**：她最晚加入、等級最低，紅利不往前放會早早被棄用（Ray）。</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>低（Ray 的設計，-1775 後確認）：連開共鬥＝輸出下降、局變長，而她的評價時間係數是 650（別人 400）⇒ 必定低評（錢是敵 HP×等第%，D 只拿 50%）。低評反而給她較多 EXP 與好感 —— 那是她「打得爛也開心」的性格，是取捨不是漏洞。</t>
+          <t>中：輸出強，但**零回血**，連戰會被耗死；評價係數 650、命中 ×0.5 是她的代價。</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>不改。她**沒有任何回血手段**（共鬥只擋不補），連戰會被慢慢耗死 ⇒ 保守型玩家會選諾薇兒不是她（Ray），「保守玩法讓她升最快」不成立。</t>
+          <t>不改（Ray）。</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>前提（ver -1775）：聖徒化／夢魘化一場限一次，回填一律下一場才生效；星不用等級鎖，價格 1/1/2/2/3/3/4/4＋⑨條件。⇒ 單體 Boss 戰三人都只有「一次變身」，差距回到技能本身；安雅的便宜強星（③烙印）只剩連戰價值。索菈娜 ⑦聚落雖然同一場能再開共鬥，但被破防值總量與評價係數 650 綁住（連開＝必定低評），Ray 定為刻意的取捨，不改。諾薇兒的免死三顆（4 份）約 Lv5 可成形，但 Boss 戰只有一次免死。</t>
+          <t>結論（ver -1779，與 Ray 對過）：三人定位清楚 —— 諾薇兒保命（②④ 約 Lv4 就免死，②⑥ 就是 MB 保證）、安雅爆發（升階＋粉碎，非夢魘粉碎只有 5 秒）、索菈娜中期輸出（循環 Lv5 成形，但零回血會被耗死）。索菈娜的循環刻意放在前面：她最晚加入、等級最低。</t>
         </is>
       </c>
     </row>
